--- a/data/trans_orig/IP74A6_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP74A6_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27721</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41228</t>
+          <t>41181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28084</t>
+          <t>28437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35694</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61566</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112359</t>
+          <t>112531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
